--- a/temp/BBVA_MASTERCARD_20250215.xlsx
+++ b/temp/BBVA_MASTERCARD_20250215.xlsx
@@ -471,8 +471,10 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>49846.4</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>49846,4</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
